--- a/output/crash_data.xlsx
+++ b/output/crash_data.xlsx
@@ -426,17 +426,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CK2"/>
+  <dimension ref="A1:CK3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="40" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="27" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
     <col width="40" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
@@ -444,32 +444,32 @@
     <col width="15" customWidth="1" min="13" max="13"/>
     <col width="20" customWidth="1" min="14" max="14"/>
     <col width="21" customWidth="1" min="15" max="15"/>
-    <col width="28" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="36" customWidth="1" min="16" max="16"/>
+    <col width="24" customWidth="1" min="17" max="17"/>
     <col width="10" customWidth="1" min="18" max="18"/>
     <col width="21" customWidth="1" min="19" max="19"/>
-    <col width="35" customWidth="1" min="20" max="20"/>
-    <col width="30" customWidth="1" min="21" max="21"/>
+    <col width="40" customWidth="1" min="20" max="20"/>
+    <col width="40" customWidth="1" min="21" max="21"/>
     <col width="23" customWidth="1" min="22" max="22"/>
     <col width="18" customWidth="1" min="23" max="23"/>
     <col width="40" customWidth="1" min="24" max="24"/>
-    <col width="19" customWidth="1" min="25" max="25"/>
-    <col width="19" customWidth="1" min="26" max="26"/>
+    <col width="22" customWidth="1" min="25" max="25"/>
+    <col width="21" customWidth="1" min="26" max="26"/>
     <col width="33" customWidth="1" min="27" max="27"/>
     <col width="18" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
-    <col width="30" customWidth="1" min="30" max="30"/>
+    <col width="40" customWidth="1" min="30" max="30"/>
     <col width="17" customWidth="1" min="31" max="31"/>
     <col width="21" customWidth="1" min="32" max="32"/>
     <col width="25" customWidth="1" min="33" max="33"/>
     <col width="16" customWidth="1" min="34" max="34"/>
     <col width="24" customWidth="1" min="35" max="35"/>
-    <col width="19" customWidth="1" min="36" max="36"/>
+    <col width="21" customWidth="1" min="36" max="36"/>
     <col width="12" customWidth="1" min="37" max="37"/>
     <col width="11" customWidth="1" min="38" max="38"/>
     <col width="15" customWidth="1" min="39" max="39"/>
     <col width="15" customWidth="1" min="40" max="40"/>
-    <col width="16" customWidth="1" min="41" max="41"/>
+    <col width="19" customWidth="1" min="41" max="41"/>
     <col width="20" customWidth="1" min="42" max="42"/>
     <col width="18" customWidth="1" min="43" max="43"/>
     <col width="13" customWidth="1" min="44" max="44"/>
@@ -478,9 +478,9 @@
     <col width="19" customWidth="1" min="47" max="47"/>
     <col width="17" customWidth="1" min="48" max="48"/>
     <col width="17" customWidth="1" min="49" max="49"/>
-    <col width="15" customWidth="1" min="50" max="50"/>
+    <col width="27" customWidth="1" min="50" max="50"/>
     <col width="13" customWidth="1" min="51" max="51"/>
-    <col width="12" customWidth="1" min="52" max="52"/>
+    <col width="18" customWidth="1" min="52" max="52"/>
     <col width="13" customWidth="1" min="53" max="53"/>
     <col width="12" customWidth="1" min="54" max="54"/>
     <col width="15" customWidth="1" min="55" max="55"/>
@@ -497,7 +497,7 @@
     <col width="17" customWidth="1" min="66" max="66"/>
     <col width="13" customWidth="1" min="67" max="67"/>
     <col width="11" customWidth="1" min="68" max="68"/>
-    <col width="29" customWidth="1" min="69" max="69"/>
+    <col width="36" customWidth="1" min="69" max="69"/>
     <col width="19" customWidth="1" min="70" max="70"/>
     <col width="19" customWidth="1" min="71" max="71"/>
     <col width="18" customWidth="1" min="72" max="72"/>
@@ -505,7 +505,7 @@
     <col width="28" customWidth="1" min="74" max="74"/>
     <col width="31" customWidth="1" min="75" max="75"/>
     <col width="15" customWidth="1" min="76" max="76"/>
-    <col width="26" customWidth="1" min="77" max="77"/>
+    <col width="28" customWidth="1" min="77" max="77"/>
     <col width="20" customWidth="1" min="78" max="78"/>
     <col width="13" customWidth="1" min="79" max="79"/>
     <col width="27" customWidth="1" min="80" max="80"/>
@@ -973,13 +973,11 @@
           <t>SVNIT Crash Data for TEST (1).pdf</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>ABC012345678 FIR Date &amp; Time : 20-Jun-2032 : 12:20 PM</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>Indian Penal Code, 1860 ,</t>
@@ -1010,15 +1008,11 @@
           <t>Harsh Kakkad</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
           <t>316 District Name : Surat</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>SVNIT, Transportation Cell</t>
@@ -1099,9 +1093,6 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr">
         <is>
           <t>Motorised Fuel Vehicle</t>
@@ -1112,13 +1103,11 @@
           <t>Car/Jeep/Van/Taxi</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="inlineStr">
         <is>
           <t>Diesel</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="inlineStr">
         <is>
           <t>NA</t>
@@ -1139,7 +1128,6 @@
           <t>19-May-2036</t>
         </is>
       </c>
-      <c r="AR2" t="inlineStr"/>
       <c r="AS2" t="inlineStr">
         <is>
           <t>5</t>
@@ -1160,36 +1148,21 @@
           <t>Hydraulic Brake</t>
         </is>
       </c>
-      <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="inlineStr">
         <is>
           <t>Front Damage</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
           <t>MIHIRKUMAR</t>
         </is>
       </c>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="inlineStr"/>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
-      <c r="BI2" t="inlineStr"/>
-      <c r="BJ2" t="inlineStr"/>
-      <c r="BK2" t="inlineStr"/>
       <c r="BL2" t="inlineStr">
         <is>
           <t>? Not Known</t>
         </is>
       </c>
-      <c r="BM2" t="inlineStr"/>
-      <c r="BN2" t="inlineStr"/>
       <c r="BO2" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -1205,19 +1178,16 @@
           <t>National Highway under NHAI</t>
         </is>
       </c>
-      <c r="BR2" t="inlineStr"/>
       <c r="BS2" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="BT2" t="inlineStr"/>
       <c r="BU2" t="inlineStr">
         <is>
           <t>(in metre) 12.50</t>
         </is>
       </c>
-      <c r="BV2" t="inlineStr"/>
       <c r="BW2" t="inlineStr">
         <is>
           <t>er devices in case of PSV Yes</t>
@@ -1238,7 +1208,6 @@
           <t>/ Barrier Type yes</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr"/>
       <c r="CB2" t="inlineStr">
         <is>
           <t>Not applicable</t>
@@ -1287,6 +1256,333 @@
       <c r="CK2" t="inlineStr">
         <is>
           <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SVNIT_Crash_Record_007.pdf</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>03:45 PM</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>03:45 PM</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Indian Penal Code, 1860, Motor Vehicles</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Section 279; Section 304A; Section 134,</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>NA Accident ID 2032880077889900</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>PALSANA POLICE STATION Investigating Mahesh Baraiya</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Palsana, Surat District, Gujarat, India Field Officer Kiran Patel</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>316 District Name Surat</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Palsana - Bardoli Highway Junction</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>3 km from Palsana Town</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Fatal</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>State Highway</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>/ Street Name SH 188, Palsana-Bardoli Road</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Roads and Buildings Department Gujarat</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Vehicle to Vehicle</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Head On</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>of accident scene Overtaking on curve</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Dangerous Overtaking</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>Cloudy with drizzle</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Daylight</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>Rural Area</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>Overtaking prohibited signs on all curves</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Motorised Fuel Vehicle</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>Goods Vehicle (LGV)</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>Diesel</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>mDI1234567CR</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>MA1AA2FRCG1234567</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>08-Dec-2032</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>05-Jan-2033</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>2680</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>BHARAT STAGE VI</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>Hydraulic Brake</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Front Damage, Roof Damage</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>JAYESHBHAI GAMIT</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr"/>
+      <c r="BB3" t="inlineStr"/>
+      <c r="BC3" t="inlineStr"/>
+      <c r="BD3" t="inlineStr"/>
+      <c r="BE3" t="inlineStr"/>
+      <c r="BF3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr"/>
+      <c r="BH3" t="inlineStr"/>
+      <c r="BI3" t="inlineStr"/>
+      <c r="BJ3" t="inlineStr"/>
+      <c r="BK3" t="inlineStr"/>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>? Not Known</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr"/>
+      <c r="BN3" t="inlineStr"/>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>State Highway Authority of Gujarat</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr"/>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr"/>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>(in metre) 7.5</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr"/>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>(in KMPH) 60-90</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>Not Available</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>Available - Non Reflective</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>/ Barrier Type No</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr"/>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="CI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CJ3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CK3" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>
